--- a/verification/cases/roundtrip/formulas_conditional/init.xlsx
+++ b/verification/cases/roundtrip/formulas_conditional/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/conditional-aggregates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F15230-6437-FD45-9C89-3D71D637B860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1A6F89C-92CD-485B-9DB9-A2E9161781D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="660" windowWidth="25680" windowHeight="17000" xr2:uid="{FA50BAF6-922D-E04C-9B6E-40FA85589285}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FA50BAF6-922D-E04C-9B6E-40FA85589285}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1025,15 +1025,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41912A79-FC6F-704F-A47E-922ADE4ED5B7}">
   <dimension ref="B2:H200"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="50.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1044,7 +1044,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1053,7 +1053,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1064,7 +1064,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
@@ -1083,7 +1083,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>10</v>
       </c>
@@ -1102,7 +1102,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>25</v>
       </c>
@@ -1119,7 +1119,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>50</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>100</v>
       </c>
@@ -1153,7 +1153,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <v>150</v>
       </c>
@@ -1170,7 +1170,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1187,7 +1187,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
@@ -1204,7 +1204,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
@@ -1221,7 +1221,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
@@ -1238,7 +1238,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
@@ -1251,7 +1251,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="e">
         <f>NA()</f>
         <v>#N/A</v>
@@ -1270,7 +1270,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="b">
         <v>1</v>
       </c>
@@ -1287,7 +1287,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1296,7 +1296,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1305,7 +1305,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
@@ -1335,7 +1335,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <v>1</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <v>2</v>
       </c>
@@ -1371,7 +1371,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>3</v>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <v>4</v>
       </c>
@@ -1407,7 +1407,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <v>5</v>
       </c>
@@ -1425,7 +1425,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <v>6</v>
       </c>
@@ -1443,7 +1443,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <v>7</v>
       </c>
@@ -1461,7 +1461,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <v>8</v>
       </c>
@@ -1479,7 +1479,7 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>9</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1506,7 +1506,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>47</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>24</v>
       </c>
@@ -1534,7 +1534,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <v>1</v>
       </c>
@@ -1552,7 +1552,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
         <v>2</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
         <v>3</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
         <v>4</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
         <v>5</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
         <v>6</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
         <v>7</v>
       </c>
@@ -1660,7 +1660,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
         <v>8</v>
       </c>
@@ -1678,7 +1678,7 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
         <v>9</v>
       </c>
@@ -1696,7 +1696,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1705,7 +1705,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>57</v>
       </c>
@@ -1716,7 +1716,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="s">
         <v>24</v>
       </c>
@@ -1733,7 +1733,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
         <v>1</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="8">
         <v>2</v>
       </c>
@@ -1769,7 +1769,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="8">
         <v>3</v>
       </c>
@@ -1787,7 +1787,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="8">
         <v>4</v>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="8">
         <v>5</v>
       </c>
@@ -1823,7 +1823,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="8">
         <v>6</v>
       </c>
@@ -1841,7 +1841,7 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
         <v>7</v>
       </c>
@@ -1859,7 +1859,7 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="8">
         <v>8</v>
       </c>
@@ -1877,7 +1877,7 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="8">
         <v>9</v>
       </c>
@@ -1895,7 +1895,7 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1904,7 +1904,7 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>73</v>
       </c>
@@ -1915,7 +1915,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="6" t="s">
         <v>24</v>
       </c>
@@ -1932,7 +1932,7 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="8">
         <v>1</v>
       </c>
@@ -1950,7 +1950,7 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="8">
         <v>2</v>
       </c>
@@ -1968,7 +1968,7 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="8">
         <v>3</v>
       </c>
@@ -1986,7 +1986,7 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="8">
         <v>4</v>
       </c>
@@ -2004,7 +2004,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="8">
         <v>5</v>
       </c>
@@ -2022,7 +2022,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="8">
         <v>6</v>
       </c>
@@ -2040,7 +2040,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="8">
         <v>7</v>
       </c>
@@ -2058,7 +2058,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="8">
         <v>8</v>
       </c>
@@ -2076,7 +2076,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="8">
         <v>9</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -2103,7 +2103,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>91</v>
       </c>
@@ -2114,7 +2114,7 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
@@ -2131,7 +2131,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
         <v>1</v>
       </c>
@@ -2149,7 +2149,7 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="8">
         <v>2</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="8">
         <v>3</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="8">
         <v>4</v>
       </c>
@@ -2203,7 +2203,7 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="8">
         <v>5</v>
       </c>
@@ -2221,7 +2221,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
         <v>6</v>
       </c>
@@ -2239,7 +2239,7 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="8">
         <v>7</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="8">
         <v>8</v>
       </c>
@@ -2275,7 +2275,7 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -2284,7 +2284,7 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="3" t="s">
         <v>101</v>
       </c>
@@ -2295,7 +2295,7 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
         <v>24</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="8">
         <v>1</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="8">
         <v>2</v>
       </c>
@@ -2348,7 +2348,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="8">
         <v>3</v>
       </c>
@@ -2366,7 +2366,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="8">
         <v>4</v>
       </c>
@@ -2384,7 +2384,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="8">
         <v>5</v>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="8">
         <v>6</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="8">
         <v>7</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="8">
         <v>8</v>
       </c>
@@ -2456,7 +2456,7 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -2465,7 +2465,7 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="3" t="s">
         <v>117</v>
       </c>
@@ -2476,7 +2476,7 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="6" t="s">
         <v>24</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="8">
         <v>1</v>
       </c>
@@ -2511,7 +2511,7 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="8">
         <v>2</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="8">
         <v>3</v>
       </c>
@@ -2547,7 +2547,7 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="8">
         <v>4</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="8">
         <v>5</v>
       </c>
@@ -2583,7 +2583,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="8">
         <v>6</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="8">
         <v>7</v>
       </c>
@@ -2619,7 +2619,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="8">
         <v>8</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="8">
         <v>9</v>
       </c>
@@ -2655,7 +2655,7 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -2664,7 +2664,7 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B102" s="3" t="s">
         <v>136</v>
       </c>
@@ -2675,7 +2675,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="6" t="s">
         <v>24</v>
       </c>
@@ -2692,7 +2692,7 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="8">
         <v>1</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="8">
         <v>2</v>
       </c>
@@ -2728,7 +2728,7 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="8">
         <v>3</v>
       </c>
@@ -2746,7 +2746,7 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="8">
         <v>4</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="8">
         <v>5</v>
       </c>
@@ -2782,7 +2782,7 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B109" s="8">
         <v>6</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="8">
         <v>7</v>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="8">
         <v>8</v>
       </c>
@@ -2836,7 +2836,7 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -2845,7 +2845,7 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B113" s="3" t="s">
         <v>152</v>
       </c>
@@ -2856,7 +2856,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B114" s="6" t="s">
         <v>24</v>
       </c>
@@ -2873,7 +2873,7 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B115" s="8">
         <v>1</v>
       </c>
@@ -2891,7 +2891,7 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B116" s="8">
         <v>2</v>
       </c>
@@ -2909,7 +2909,7 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B117" s="8">
         <v>3</v>
       </c>
@@ -2927,7 +2927,7 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B118" s="8">
         <v>4</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B119" s="8">
         <v>5</v>
       </c>
@@ -2963,7 +2963,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B120" s="8">
         <v>6</v>
       </c>
@@ -2981,7 +2981,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B121" s="8">
         <v>7</v>
       </c>
@@ -2999,7 +2999,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B122" s="8">
         <v>8</v>
       </c>
@@ -3017,7 +3017,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -3026,7 +3026,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -3035,7 +3035,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -3044,7 +3044,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -3053,7 +3053,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -3062,7 +3062,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -3071,7 +3071,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -3080,7 +3080,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -3089,7 +3089,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -3098,7 +3098,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -3107,7 +3107,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -3116,7 +3116,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -3125,7 +3125,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -3134,7 +3134,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -3143,7 +3143,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -3152,7 +3152,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -3161,7 +3161,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -3170,7 +3170,7 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -3179,7 +3179,7 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -3188,7 +3188,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -3197,7 +3197,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -3206,7 +3206,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -3215,7 +3215,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -3224,7 +3224,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -3233,7 +3233,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -3242,7 +3242,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -3251,7 +3251,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -3260,7 +3260,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -3269,7 +3269,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -3278,7 +3278,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -3287,7 +3287,7 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -3296,7 +3296,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -3305,7 +3305,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -3314,7 +3314,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -3323,7 +3323,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -3332,7 +3332,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -3341,7 +3341,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -3350,7 +3350,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -3359,7 +3359,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -3368,7 +3368,7 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -3377,7 +3377,7 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -3386,7 +3386,7 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -3395,7 +3395,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -3404,7 +3404,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -3413,7 +3413,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -3422,7 +3422,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -3431,7 +3431,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -3440,7 +3440,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -3449,7 +3449,7 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -3458,7 +3458,7 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -3467,7 +3467,7 @@
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -3476,7 +3476,7 @@
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -3485,7 +3485,7 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -3494,7 +3494,7 @@
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -3503,7 +3503,7 @@
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -3512,7 +3512,7 @@
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -3521,7 +3521,7 @@
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -3530,7 +3530,7 @@
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -3539,7 +3539,7 @@
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -3548,7 +3548,7 @@
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -3557,7 +3557,7 @@
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
     </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -3566,7 +3566,7 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -3575,7 +3575,7 @@
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
     </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -3584,7 +3584,7 @@
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
     </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -3593,7 +3593,7 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -3602,7 +3602,7 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -3611,7 +3611,7 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -3620,7 +3620,7 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -3629,7 +3629,7 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -3638,7 +3638,7 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -3647,7 +3647,7 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -3656,7 +3656,7 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -3665,7 +3665,7 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
     </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -3674,7 +3674,7 @@
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
     </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -3683,7 +3683,7 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
     </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -3692,7 +3692,7 @@
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
     </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -3701,7 +3701,7 @@
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
     </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -3710,7 +3710,7 @@
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
     </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
